--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484848_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484848_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5649</v>
+        <v>3.6039</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8454</v>
+        <v>1.9373</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7196</v>
+        <v>1.6667</v>
       </c>
       <c r="G2" t="n">
         <v>3.3086</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.121</v>
+        <v>-0.082</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.7048</v>
+        <v>-0.6129</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5838</v>
+        <v>0.5309</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1258</v>
+        <v>0.8302</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4049</v>
+        <v>-0.7055</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7208</v>
+        <v>1.5357</v>
       </c>
       <c r="G3" t="n">
         <v>-1.7879</v>
@@ -688,13 +688,13 @@
         <v>0.5661</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7441</v>
+        <v>1.4485</v>
       </c>
       <c r="T3" t="n">
-        <v>1.9516</v>
+        <v>0.8411999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7925</v>
+        <v>0.6073</v>
       </c>
       <c r="V3" t="n">
         <v>1.547</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VALERO CHICA</t>
+          <t>J. MERENCIO MORENO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1935</v>
+        <v>0.7006</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3385</v>
+        <v>-1.1522</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.145</v>
+        <v>1.8528</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.547</v>
+        <v>-0.7989000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.9283</v>
+        <v>-0.342</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3814</v>
+        <v>-0.457</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0258</v>
+        <v>0.0699</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4634</v>
+        <v>0.5705</v>
       </c>
       <c r="L4" t="n">
-        <v>1.4892</v>
+        <v>-0.5006</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5728</v>
+        <v>-0.8688</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.465</v>
+        <v>-0.9125</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1078</v>
+        <v>0.0437</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0987</v>
+        <v>-0.2553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2562</v>
+        <v>-0.5804</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8425</v>
+        <v>0.3252</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8678</v>
+        <v>0.6226</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8678</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4172</v>
+        <v>0.0818</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.3603</v>
+        <v>-0.7554999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9431</v>
+        <v>0.8373</v>
       </c>
       <c r="G5" t="n">
         <v>0.7615</v>
@@ -844,13 +844,13 @@
         <v>2.0757</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7448</v>
+        <v>-0.2459</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1634</v>
+        <v>-0.5587</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4186</v>
+        <v>0.3128</v>
       </c>
       <c r="V5" t="n">
         <v>-0.6226</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MERENCIO MORENO</t>
+          <t>J. VALERO CHICA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.823</v>
+        <v>-0.4768</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1467</v>
+        <v>-0.2259</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3237</v>
+        <v>-0.2508</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.547</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.342</v>
+        <v>-1.9283</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.457</v>
+        <v>1.3814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0699</v>
+        <v>1.0258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5705</v>
+        <v>-0.4634</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5006</v>
+        <v>1.4892</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8688</v>
+        <v>-1.5728</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9125</v>
+        <v>-1.465</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0437</v>
+        <v>-0.1078</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0757</v>
+        <v>2.4531</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.7789</v>
+        <v>0.4284</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.5749</v>
+        <v>-0.3083</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2039</v>
+        <v>0.7367</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6226</v>
+        <v>-1.8678</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3208</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9368</v>
+        <v>-0.8935999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9065</v>
+        <v>-1.1014</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0303</v>
+        <v>0.2078</v>
       </c>
       <c r="G7" t="n">
         <v>-0.824</v>
@@ -1000,13 +1000,13 @@
         <v>0.7548</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5467</v>
+        <v>-0.5034999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0559</v>
+        <v>-0.2508</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4908</v>
+        <v>-0.2527</v>
       </c>
       <c r="V7" t="n">
         <v>0.6226</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0243</v>
+        <v>-1.1693</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3561</v>
+        <v>-0.7127</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6682</v>
+        <v>-0.4566</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2488</v>
@@ -1078,13 +1078,13 @@
         <v>0.5661</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0963</v>
+        <v>-0.2413</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8818</v>
+        <v>-0.2384</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2145</v>
+        <v>-0.0029</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2452</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0778</v>
+        <v>-2.232</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2742</v>
+        <v>-1.5077</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8037</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0.07969999999999999</v>
@@ -1156,13 +1156,13 @@
         <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9746</v>
+        <v>0.8205</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7236</v>
+        <v>0.4901</v>
       </c>
       <c r="U9" t="n">
-        <v>0.251</v>
+        <v>0.3304</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2452</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2446</v>
+        <v>-2.6995</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5502</v>
+        <v>-2.9786</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3055</v>
+        <v>0.2791</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7544</v>
@@ -1234,13 +1234,13 @@
         <v>0.5661</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7742</v>
+        <v>0.3193</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.4592</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1134</v>
+        <v>-0.1399</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3229</v>
+        <v>-3.826</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4293</v>
+        <v>-3.3504</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1064</v>
+        <v>-0.4756</v>
       </c>
       <c r="G11" t="n">
         <v>-3.4982</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1187</v>
+        <v>0.6156</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1357</v>
+        <v>0.2146</v>
       </c>
       <c r="U11" t="n">
-        <v>0.983</v>
+        <v>0.401</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9434</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.962400000000001</v>
+        <v>-6.0807</v>
       </c>
       <c r="E12" t="n">
-        <v>-11.4345</v>
+        <v>-10.5526</v>
       </c>
       <c r="F12" t="n">
-        <v>4.471900000000001</v>
+        <v>4.472099999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-4.3094</v>
@@ -1381,7 +1381,7 @@
         <v>3.3583</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9434999999999998</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q12" t="n">
         <v>-15.096</v>
@@ -1390,13 +1390,13 @@
         <v>14.1525</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4226</v>
+        <v>2.3043</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4261</v>
+        <v>-0.5444000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>2.848800000000001</v>
+        <v>2.8488</v>
       </c>
       <c r="V12" t="n">
         <v>-3.132</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1376</v>
+        <v>3.8521</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5116</v>
+        <v>2.0962</v>
       </c>
       <c r="F13" t="n">
-        <v>1.626</v>
+        <v>1.7559</v>
       </c>
       <c r="G13" t="n">
         <v>3.6273</v>
@@ -1468,13 +1468,13 @@
         <v>1.887</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3949</v>
+        <v>-0.6804</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3521</v>
+        <v>-0.7675</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0428</v>
+        <v>0.0871</v>
       </c>
       <c r="V13" t="n">
         <v>2.7922</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9796</v>
+        <v>3.3235</v>
       </c>
       <c r="E14" t="n">
         <v>2.7722</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2074</v>
+        <v>0.5513</v>
       </c>
       <c r="G14" t="n">
         <v>2.7844</v>
@@ -1546,13 +1546,13 @@
         <v>0.7548</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5596</v>
+        <v>-0.2157</v>
       </c>
       <c r="T14" t="n">
         <v>0.0029</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5625</v>
+        <v>-0.2186</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8383</v>
+        <v>2.4004</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3213</v>
+        <v>1.5418</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5171</v>
+        <v>0.8586</v>
       </c>
       <c r="G15" t="n">
         <v>1.3588</v>
@@ -1624,13 +1624,13 @@
         <v>2.2644</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9699</v>
+        <v>0.532</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9616</v>
+        <v>0.1822</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0083</v>
+        <v>0.3498</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6226</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4514</v>
+        <v>1.9362</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1441</v>
+        <v>0.6312</v>
       </c>
       <c r="F16" t="n">
-        <v>1.3073</v>
+        <v>1.305</v>
       </c>
       <c r="G16" t="n">
         <v>0.869</v>
@@ -1702,13 +1702,13 @@
         <v>2.0757</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6819</v>
+        <v>-0.197</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0458</v>
+        <v>-0.5587</v>
       </c>
       <c r="U16" t="n">
-        <v>0.364</v>
+        <v>0.3616</v>
       </c>
       <c r="V16" t="n">
         <v>0.3208</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3256</v>
+        <v>1.3052</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3382</v>
+        <v>0.2408</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9874000000000001</v>
+        <v>1.0644</v>
       </c>
       <c r="G17" t="n">
         <v>0.09619999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.887</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4497</v>
+        <v>-0.4701</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3375</v>
+        <v>-0.4349</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1122</v>
+        <v>-0.0352</v>
       </c>
       <c r="V17" t="n">
         <v>1.8678</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5929</v>
+        <v>0.5329</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.198</v>
+        <v>-1.8083</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7908</v>
+        <v>2.3411</v>
       </c>
       <c r="G19" t="n">
         <v>0.2864</v>
@@ -1936,13 +1936,13 @@
         <v>0.7548</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1552</v>
+        <v>0.0953</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.823</v>
+        <v>-0.4333</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.5285</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6036</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.756</v>
+        <v>-0.7861</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.131</v>
+        <v>-1.4233</v>
       </c>
       <c r="F20" t="n">
-        <v>0.375</v>
+        <v>0.6372</v>
       </c>
       <c r="G20" t="n">
         <v>1.288</v>
@@ -2014,13 +2014,13 @@
         <v>1.887</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2892</v>
+        <v>-0.3193</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0407</v>
+        <v>-0.333</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2486</v>
+        <v>0.0136</v>
       </c>
       <c r="V20" t="n">
         <v>-0.6226</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. CARRION GALINDO</t>
+          <t>D. KEITA DIALLO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1499</v>
+        <v>-1.3226</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1073</v>
+        <v>-2.2627</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9574</v>
+        <v>0.9401</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2281</v>
+        <v>-1.2762</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9485</v>
+        <v>0.0877</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2796</v>
+        <v>-1.3638</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.1079</v>
+        <v>-1.1457</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8499</v>
+        <v>-0.4962</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.258</v>
+        <v>-0.6496</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1202</v>
+        <v>-0.1304</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.09859999999999999</v>
+        <v>0.5838</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0216</v>
+        <v>-0.7143</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0781</v>
+        <v>-0.0465</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1328</v>
+        <v>-0.1735</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9453</v>
+        <v>0.127</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. KEITA DIALLO</t>
+          <t>H. RIVAS OSETE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3226</v>
+        <v>-1.4642</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2627</v>
+        <v>-1.5297</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9401</v>
+        <v>0.0655</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2762</v>
+        <v>-1.55</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0877</v>
+        <v>-1.3985</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3638</v>
+        <v>-0.1515</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1457</v>
+        <v>-1.2357</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4962</v>
+        <v>-1.2357</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1304</v>
+        <v>-0.3143</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5838</v>
+        <v>-0.1628</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7143</v>
+        <v>-0.1515</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3774</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0465</v>
+        <v>-0.2916</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1735</v>
+        <v>-0.2939</v>
       </c>
       <c r="U22" t="n">
-        <v>0.127</v>
+        <v>0.0024</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>H. RIVAS OSETE</t>
+          <t>L. CARRION GALINDO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5435</v>
+        <v>-1.6442</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5297</v>
+        <v>-3.2047</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0139</v>
+        <v>1.5605</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.55</v>
+        <v>-2.2281</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3985</v>
+        <v>-0.9485</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1515</v>
+        <v>-1.2796</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2357</v>
+        <v>-2.1079</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2357</v>
+        <v>-0.8499</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.258</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3143</v>
+        <v>-0.1202</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1628</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.1515</v>
+        <v>-0.0216</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3774</v>
+        <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3709</v>
+        <v>0.5839</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2939</v>
+        <v>0.0354</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.077</v>
+        <v>0.5485</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.8417</v>
+        <v>-1.772</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5815</v>
+        <v>-2.7764</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7399</v>
+        <v>1.0044</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1973</v>
@@ -2326,13 +2326,13 @@
         <v>1.1322</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1669</v>
+        <v>0.2366</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1205</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0465</v>
+        <v>0.311</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>6.9626</v>
+        <v>7.6121</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.4719</v>
+        <v>-4.472</v>
       </c>
       <c r="F25" t="n">
-        <v>11.4345</v>
+        <v>12.084</v>
       </c>
       <c r="G25" t="n">
-        <v>4.309400000000002</v>
+        <v>4.3094</v>
       </c>
       <c r="H25" t="n">
         <v>13.0773</v>
@@ -2404,13 +2404,13 @@
         <v>15.096</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4226</v>
+        <v>-0.7727999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.8487</v>
+        <v>-2.848699999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4263</v>
+        <v>2.0757</v>
       </c>
       <c r="V25" t="n">
         <v>3.132</v>
